--- a/braph2individualconnectome/pipelines/neuroimaging conversion PDFs/Example data NIfTI PDF shape covariation/reference_data/pdf_gmprob/sub-0009_ses-01_GMprob_pdf.xlsx
+++ b/braph2individualconnectome/pipelines/neuroimaging conversion PDFs/Example data NIfTI PDF shape covariation/reference_data/pdf_gmprob/sub-0009_ses-01_GMprob_pdf.xlsx
@@ -1,7 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -11415,7 +11414,7 @@
         <v>0.21309728710761394</v>
       </c>
       <c r="E32" s="0">
-        <v>0.27100271002710003</v>
+        <v>0.27100271002710002</v>
       </c>
       <c r="F32" s="0">
         <v>0.15494533872772648</v>
@@ -11768,7 +11767,7 @@
         <v>0</v>
       </c>
       <c r="B33" s="0">
-        <v>0.17561465127947804</v>
+        <v>0.17561465127947803</v>
       </c>
       <c r="C33" s="0">
         <v>0.50375607600530226</v>
@@ -12041,7 +12040,7 @@
         <v>0</v>
       </c>
       <c r="CO33" s="0">
-        <v>0.066120074054482878</v>
+        <v>0.066120074054482877</v>
       </c>
       <c r="CP33" s="0">
         <v>0</v>
@@ -12513,7 +12512,7 @@
         <v>0</v>
       </c>
       <c r="I35" s="0">
-        <v>0.44850498338870643</v>
+        <v>0.44850498338870642</v>
       </c>
       <c r="J35" s="0">
         <v>0</v>
@@ -13501,7 +13500,7 @@
         <v>0</v>
       </c>
       <c r="CS37" s="0">
-        <v>0.044228217602830571</v>
+        <v>0.04422821760283057</v>
       </c>
       <c r="CT37" s="0">
         <v>0</v>
@@ -13698,7 +13697,7 @@
         <v>0</v>
       </c>
       <c r="AP38" s="0">
-        <v>1.72185430463576</v>
+        <v>1.7218543046357599</v>
       </c>
       <c r="AQ38" s="0">
         <v>0.042918454935622276</v>
@@ -14703,7 +14702,7 @@
         <v>8.3489096573209114</v>
       </c>
       <c r="O41" s="0">
-        <v>8.3250939292070783</v>
+        <v>8.3250939292070782</v>
       </c>
       <c r="P41" s="0">
         <v>12.898822726497245</v>
@@ -14832,7 +14831,7 @@
         <v>11.954992967651252</v>
       </c>
       <c r="BF41" s="0">
-        <v>0.1665972511453569</v>
+        <v>0.16659725114535689</v>
       </c>
       <c r="BG41" s="0">
         <v>0</v>
@@ -14898,7 +14897,7 @@
         <v>0</v>
       </c>
       <c r="CB41" s="0">
-        <v>3.6220472440945049</v>
+        <v>3.6220472440945048</v>
       </c>
       <c r="CC41" s="0">
         <v>0</v>
@@ -15200,7 +15199,7 @@
         <v>0</v>
       </c>
       <c r="BH42" s="0">
-        <v>0.97054886211512626</v>
+        <v>0.97054886211512625</v>
       </c>
       <c r="BI42" s="0">
         <v>0</v>
@@ -15514,7 +15513,7 @@
         <v>15.021459227467799</v>
       </c>
       <c r="AR43" s="0">
-        <v>1.3084112149532699</v>
+        <v>1.3084112149532698</v>
       </c>
       <c r="AS43" s="0">
         <v>2.3809523809523787</v>
@@ -15526,7 +15525,7 @@
         <v>0.29673590504451014</v>
       </c>
       <c r="AV43" s="0">
-        <v>2.5262687234518198</v>
+        <v>2.5262687234518197</v>
       </c>
       <c r="AW43" s="0">
         <v>0.08073196986006452</v>
@@ -15598,7 +15597,7 @@
         <v>6.7611777535441604</v>
       </c>
       <c r="BT43" s="0">
-        <v>7.5807682523530851</v>
+        <v>7.580768252353085</v>
       </c>
       <c r="BU43" s="0">
         <v>0</v>
@@ -15703,10 +15702,10 @@
         <v>0</v>
       </c>
       <c r="DC43" s="0">
-        <v>2.8513695554557677</v>
+        <v>2.8513695554557676</v>
       </c>
       <c r="DD43" s="0">
-        <v>0.2185792349726774</v>
+        <v>0.21857923497267739</v>
       </c>
       <c r="DE43" s="0">
         <v>11.599806669888824</v>
@@ -15736,7 +15735,7 @@
         <v>0</v>
       </c>
       <c r="DN43" s="0">
-        <v>0.58593749999999945</v>
+        <v>0.58593749999999944</v>
       </c>
       <c r="DO43" s="0">
         <v>0</v>
@@ -15768,7 +15767,7 @@
         <v>0</v>
       </c>
       <c r="H44" s="0">
-        <v>1.9981834695731136</v>
+        <v>1.9981834695731135</v>
       </c>
       <c r="I44" s="0">
         <v>0.099667774086378641</v>
@@ -15900,13 +15899,13 @@
         <v>0</v>
       </c>
       <c r="AZ44" s="0">
-        <v>7.1507965913301153</v>
+        <v>7.1507965913301152</v>
       </c>
       <c r="BA44" s="0">
         <v>11.764705882352931</v>
       </c>
       <c r="BB44" s="0">
-        <v>6.327616794795973</v>
+        <v>6.3276167947959729</v>
       </c>
       <c r="BC44" s="0">
         <v>1.117318435754189</v>
@@ -16011,7 +16010,7 @@
         <v>14.642631246046793</v>
       </c>
       <c r="CK44" s="0">
-        <v>0.33205619412515936</v>
+        <v>0.33205619412515935</v>
       </c>
       <c r="CL44" s="0">
         <v>0.075786282682834341</v>
@@ -16190,7 +16189,7 @@
         <v>0</v>
       </c>
       <c r="AB45" s="0">
-        <v>1.1036174126302874</v>
+        <v>1.1036174126302873</v>
       </c>
       <c r="AC45" s="0">
         <v>4.3262411347517693</v>
@@ -16199,7 +16198,7 @@
         <v>1.4275517487508909</v>
       </c>
       <c r="AE45" s="0">
-        <v>0.20491803278688509</v>
+        <v>0.20491803278688508</v>
       </c>
       <c r="AF45" s="0">
         <v>0</v>
@@ -16295,7 +16294,7 @@
         <v>1.0945273631840786</v>
       </c>
       <c r="BK45" s="0">
-        <v>3.111477436637129</v>
+        <v>3.1114774366371289</v>
       </c>
       <c r="BL45" s="0">
         <v>5.0630492930836795</v>
@@ -16651,7 +16650,7 @@
         <v>15.06024096385541</v>
       </c>
       <c r="BI46" s="0">
-        <v>0.032275416890801476</v>
+        <v>0.032275416890801475</v>
       </c>
       <c r="BJ46" s="0">
         <v>0.2321724709784409</v>
@@ -16902,7 +16901,7 @@
         <v>14.205128205128272</v>
       </c>
       <c r="X47" s="0">
-        <v>3.9226833428084325</v>
+        <v>3.9226833428084324</v>
       </c>
       <c r="Y47" s="0">
         <v>0.31446540880503293</v>
@@ -17261,7 +17260,7 @@
         <v>0.091911764705882276</v>
       </c>
       <c r="W48" s="0">
-        <v>9.282051282051274</v>
+        <v>9.2820512820512739</v>
       </c>
       <c r="X48" s="0">
         <v>1.5349630471858997</v>
@@ -17288,7 +17287,7 @@
         <v>6.9672131147540917</v>
       </c>
       <c r="AF48" s="0">
-        <v>6.5263157894736788</v>
+        <v>6.5263157894736787</v>
       </c>
       <c r="AG48" s="0">
         <v>14.463558171118141</v>
@@ -17297,7 +17296,7 @@
         <v>0.49952426260704053</v>
       </c>
       <c r="AI48" s="0">
-        <v>3.6485253876558193</v>
+        <v>3.6485253876558192</v>
       </c>
       <c r="AJ48" s="0">
         <v>14.117647058823517</v>
@@ -17519,7 +17518,7 @@
         <v>13.934426229508183</v>
       </c>
       <c r="DE48" s="0">
-        <v>0.096665055582406873</v>
+        <v>0.096665055582406872</v>
       </c>
       <c r="DF48" s="0">
         <v>0.56237218813905887</v>
@@ -17869,7 +17868,7 @@
         <v>0.41948263807970132</v>
       </c>
       <c r="DA49" s="0">
-        <v>0.36023054755043194</v>
+        <v>0.36023054755043193</v>
       </c>
       <c r="DB49" s="0">
         <v>0</v>
@@ -18180,7 +18179,7 @@
         <v>4.6589018302828578</v>
       </c>
       <c r="CJ50" s="0">
-        <v>0.031625553447185297</v>
+        <v>0.031625553447185296</v>
       </c>
       <c r="CK50" s="0">
         <v>7.3307790549169791</v>
@@ -18231,7 +18230,7 @@
         <v>0.069913773013283553</v>
       </c>
       <c r="DA50" s="0">
-        <v>2.0893371757925055</v>
+        <v>2.0893371757925054</v>
       </c>
       <c r="DB50" s="0">
         <v>0.23510971786833837</v>
@@ -18359,7 +18358,7 @@
         <v>0.068634179821551067</v>
       </c>
       <c r="AA51" s="0">
-        <v>17.590149516270874</v>
+        <v>17.590149516270873</v>
       </c>
       <c r="AB51" s="0">
         <v>4.5984058859595303</v>
@@ -18443,7 +18442,7 @@
         <v>0.088704908338261307</v>
       </c>
       <c r="BC51" s="0">
-        <v>0.86338242762823692</v>
+        <v>0.86338242762823691</v>
       </c>
       <c r="BD51" s="0">
         <v>0</v>
@@ -18488,7 +18487,7 @@
         <v>0</v>
       </c>
       <c r="BR51" s="0">
-        <v>5.8852022281424024</v>
+        <v>5.8852022281424023</v>
       </c>
       <c r="BS51" s="0">
         <v>0.036350418029807312</v>
@@ -18542,7 +18541,7 @@
         <v>1.0648918469217961</v>
       </c>
       <c r="CJ51" s="0">
-        <v>0.031625553447185297</v>
+        <v>0.031625553447185296</v>
       </c>
       <c r="CK51" s="0">
         <v>2.5798212005108532</v>
@@ -18632,7 +18631,7 @@
         <v>8.9743589743589656</v>
       </c>
       <c r="DN51" s="0">
-        <v>0.58593749999999945</v>
+        <v>0.58593749999999944</v>
       </c>
       <c r="DO51" s="0">
         <v>16.019417475728144</v>
@@ -18964,7 +18963,7 @@
         <v>0</v>
       </c>
       <c r="DD52" s="0">
-        <v>0.2185792349726774</v>
+        <v>0.21857923497267739</v>
       </c>
       <c r="DE52" s="0">
         <v>0</v>
@@ -18973,7 +18972,7 @@
         <v>0</v>
       </c>
       <c r="DG52" s="0">
-        <v>14.024390243902428</v>
+        <v>14.024390243902427</v>
       </c>
       <c r="DH52" s="0">
         <v>13.636363636363622</v>
@@ -19098,7 +19097,7 @@
         <v>4.3032786885245864</v>
       </c>
       <c r="AF53" s="0">
-        <v>1.6842105263157881</v>
+        <v>1.684210526315788</v>
       </c>
       <c r="AG53" s="0">
         <v>0.29425079221367106</v>
@@ -19143,7 +19142,7 @@
         <v>2.8380634390651061</v>
       </c>
       <c r="AU53" s="0">
-        <v>0.037091988130563768</v>
+        <v>0.037091988130563767</v>
       </c>
       <c r="AV53" s="0">
         <v>0</v>
@@ -19299,7 +19298,7 @@
         <v>0</v>
       </c>
       <c r="CU53" s="0">
-        <v>20.359281437125731</v>
+        <v>20.35928143712573</v>
       </c>
       <c r="CV53" s="0">
         <v>11.753731343283572</v>
@@ -19439,7 +19438,7 @@
         <v>0</v>
       </c>
       <c r="Y54" s="0">
-        <v>3.1446540880503116</v>
+        <v>3.1446540880503115</v>
       </c>
       <c r="Z54" s="0">
         <v>0</v>
@@ -19819,7 +19818,7 @@
         <v>0</v>
       </c>
       <c r="AE55" s="0">
-        <v>0.20491803278688509</v>
+        <v>0.20491803278688508</v>
       </c>
       <c r="AF55" s="0">
         <v>0.42105263157894701</v>
@@ -24971,7 +24970,7 @@
         <v>0</v>
       </c>
       <c r="BG69" s="0">
-        <v>0.16635859519408675</v>
+        <v>0.16635859519408674</v>
       </c>
       <c r="BH69" s="0">
         <v>0</v>
@@ -25360,7 +25359,7 @@
         <v>0</v>
       </c>
       <c r="BP70" s="0">
-        <v>0.022045855379188691</v>
+        <v>0.02204585537918869</v>
       </c>
       <c r="BQ70" s="0">
         <v>0</v>
@@ -25662,7 +25661,7 @@
         <v>0.72329376854599337</v>
       </c>
       <c r="AV71" s="0">
-        <v>0.17885088307623504</v>
+        <v>0.17885088307623503</v>
       </c>
       <c r="AW71" s="0">
         <v>1.9106566200215267</v>
@@ -26311,7 +26310,7 @@
         <v>0</v>
       </c>
       <c r="W73" s="0">
-        <v>0.20512820512820496</v>
+        <v>0.20512820512820495</v>
       </c>
       <c r="X73" s="0">
         <v>0</v>
@@ -26374,7 +26373,7 @@
         <v>0</v>
       </c>
       <c r="AR73" s="0">
-        <v>0.037383177570093421</v>
+        <v>0.03738317757009342</v>
       </c>
       <c r="AS73" s="0">
         <v>0</v>
@@ -26446,7 +26445,7 @@
         <v>0.97939885173927643</v>
       </c>
       <c r="BP73" s="0">
-        <v>3.5934744268077568</v>
+        <v>3.5934744268077567</v>
       </c>
       <c r="BQ73" s="0">
         <v>0.035893754486719283</v>
@@ -26847,7 +26846,7 @@
         <v>0</v>
       </c>
       <c r="CC74" s="0">
-        <v>0.07499062617172847</v>
+        <v>0.074990626171728469</v>
       </c>
       <c r="CD74" s="0">
         <v>0</v>
@@ -26889,7 +26888,7 @@
         <v>0.059959227725146849</v>
       </c>
       <c r="CQ74" s="0">
-        <v>0.032509752925877739</v>
+        <v>0.032509752925877738</v>
       </c>
       <c r="CR74" s="0">
         <v>1.9654841802492791</v>
@@ -27209,7 +27208,7 @@
         <v>0</v>
       </c>
       <c r="CC75" s="0">
-        <v>0.89988751406074175</v>
+        <v>0.89988751406074174</v>
       </c>
       <c r="CD75" s="0">
         <v>0</v>
@@ -27251,7 +27250,7 @@
         <v>0.40772274853099855</v>
       </c>
       <c r="CQ75" s="0">
-        <v>0.16254876462938867</v>
+        <v>0.16254876462938866</v>
       </c>
       <c r="CR75" s="0">
         <v>5.9124320869287255</v>
@@ -27275,7 +27274,7 @@
         <v>0</v>
       </c>
       <c r="CY75" s="0">
-        <v>0.26744468757597834</v>
+        <v>0.26744468757597833</v>
       </c>
       <c r="CZ75" s="0">
         <v>4.2880447448147248</v>
@@ -27311,7 +27310,7 @@
         <v>11.788617886178852</v>
       </c>
       <c r="DK75" s="0">
-        <v>8.1830790568654575</v>
+        <v>8.1830790568654574</v>
       </c>
       <c r="DL75" s="0">
         <v>0</v>
@@ -27619,7 +27618,7 @@
         <v>10.306807286673049</v>
       </c>
       <c r="CS76" s="0">
-        <v>0.044228217602830571</v>
+        <v>0.04422821760283057</v>
       </c>
       <c r="CT76" s="0">
         <v>1.5418502202643158</v>
@@ -27658,7 +27657,7 @@
         <v>4.7365877235379372</v>
       </c>
       <c r="DF76" s="0">
-        <v>5.5725971370143102</v>
+        <v>5.5725971370143101</v>
       </c>
       <c r="DG76" s="0">
         <v>1.5243902439024377</v>
@@ -27786,7 +27785,7 @@
         <v>0</v>
       </c>
       <c r="AF77" s="0">
-        <v>2.7368421052631558</v>
+        <v>2.7368421052631557</v>
       </c>
       <c r="AG77" s="0">
         <v>0.11317338162064272</v>
@@ -27933,7 +27932,7 @@
         <v>0.15748031496062978</v>
       </c>
       <c r="CC77" s="0">
-        <v>7.3115860517435261</v>
+        <v>7.311586051743526</v>
       </c>
       <c r="CD77" s="0">
         <v>0.65384615384615319</v>
@@ -28026,7 +28025,7 @@
         <v>7.3170731707317005</v>
       </c>
       <c r="DH77" s="0">
-        <v>9.3582887700534681</v>
+        <v>9.358288770053468</v>
       </c>
       <c r="DI77" s="0">
         <v>0</v>
@@ -28124,10 +28123,10 @@
         <v>11.025641025641015</v>
       </c>
       <c r="X78" s="0">
-        <v>4.6617396247868062</v>
+        <v>4.6617396247868061</v>
       </c>
       <c r="Y78" s="0">
-        <v>0.94339622641509347</v>
+        <v>0.94339622641509346</v>
       </c>
       <c r="Z78" s="0">
         <v>2.3335621139327363</v>
@@ -28235,7 +28234,7 @@
         <v>0.016733601070950455</v>
       </c>
       <c r="BI78" s="0">
-        <v>2.4314147391070447</v>
+        <v>2.4314147391070446</v>
       </c>
       <c r="BJ78" s="0">
         <v>1.0281923714759527</v>
@@ -28325,7 +28324,7 @@
         <v>7.7586206896551655</v>
       </c>
       <c r="CM78" s="0">
-        <v>7.3225265511458853</v>
+        <v>7.3225265511458852</v>
       </c>
       <c r="CN78" s="0">
         <v>4.8815506101938224</v>
@@ -28376,7 +28375,7 @@
         <v>0.044903457566232555</v>
       </c>
       <c r="DD78" s="0">
-        <v>9.5628415300546355</v>
+        <v>9.5628415300546354</v>
       </c>
       <c r="DE78" s="0">
         <v>13.291445142580946</v>
@@ -28573,7 +28572,7 @@
         <v>9.1144868469803555</v>
       </c>
       <c r="BA79" s="0">
-        <v>9.1852783894306303</v>
+        <v>9.1852783894306302</v>
       </c>
       <c r="BB79" s="0">
         <v>0.65050266114724964</v>
@@ -28920,7 +28919,7 @@
         <v>0.018545994065281884</v>
       </c>
       <c r="AV80" s="0">
-        <v>0.17885088307623504</v>
+        <v>0.17885088307623503</v>
       </c>
       <c r="AW80" s="0">
         <v>0</v>
@@ -28983,7 +28982,7 @@
         <v>0.19841269841269824</v>
       </c>
       <c r="BQ80" s="0">
-        <v>9.2605886575735728</v>
+        <v>9.2605886575735727</v>
       </c>
       <c r="BR80" s="0">
         <v>0</v>
@@ -29067,7 +29066,7 @@
         <v>1.7737296260786179</v>
       </c>
       <c r="CS80" s="0">
-        <v>7.0322865988500603</v>
+        <v>7.0322865988500602</v>
       </c>
       <c r="CT80" s="0">
         <v>9.7917501001201366</v>
@@ -29088,7 +29087,7 @@
         <v>0</v>
       </c>
       <c r="CZ80" s="0">
-        <v>3.0062922395711929</v>
+        <v>3.0062922395711928</v>
       </c>
       <c r="DA80" s="0">
         <v>0.50432276657060471</v>
@@ -29779,10 +29778,10 @@
         <v>5.1328068916009135</v>
       </c>
       <c r="CO82" s="0">
-        <v>8.7014017455700437</v>
+        <v>8.7014017455700436</v>
       </c>
       <c r="CP82" s="0">
-        <v>1.4270296198585109</v>
+        <v>1.4270296198585108</v>
       </c>
       <c r="CQ82" s="0">
         <v>3.8361508452536155</v>
@@ -30078,7 +30077,7 @@
         <v>0.060584030049678855</v>
       </c>
       <c r="BT83" s="0">
-        <v>4.9732892393792883</v>
+        <v>4.9732892393792882</v>
       </c>
       <c r="BU83" s="0">
         <v>3.2639104755983803</v>
@@ -30114,7 +30113,7 @@
         <v>0.3809523809523806</v>
       </c>
       <c r="CF83" s="0">
-        <v>2.2452504317789273</v>
+        <v>2.2452504317789272</v>
       </c>
       <c r="CG83" s="0">
         <v>0.40772912604148165</v>
@@ -30123,7 +30122,7 @@
         <v>0</v>
       </c>
       <c r="CI83" s="0">
-        <v>1.7970049916805309</v>
+        <v>1.7970049916805308</v>
       </c>
       <c r="CJ83" s="0">
         <v>3.0993042378241591</v>
@@ -30138,7 +30137,7 @@
         <v>0</v>
       </c>
       <c r="CN83" s="0">
-        <v>1.9023689877961219</v>
+        <v>1.9023689877961218</v>
       </c>
       <c r="CO83" s="0">
         <v>12.509918011108162</v>
@@ -30189,7 +30188,7 @@
         <v>0</v>
       </c>
       <c r="DE83" s="0">
-        <v>0.1449975833736103</v>
+        <v>0.14499758337361029</v>
       </c>
       <c r="DF83" s="0">
         <v>0</v>
@@ -30356,7 +30355,7 @@
         <v>5.0643776824034292</v>
       </c>
       <c r="AR84" s="0">
-        <v>0.037383177570093421</v>
+        <v>0.03738317757009342</v>
       </c>
       <c r="AS84" s="0">
         <v>9.920634920634912</v>
@@ -30485,7 +30484,7 @@
         <v>0</v>
       </c>
       <c r="CI84" s="0">
-        <v>0.26622296173044902</v>
+        <v>0.26622296173044901</v>
       </c>
       <c r="CJ84" s="0">
         <v>7.3055028462998042</v>
@@ -30509,7 +30508,7 @@
         <v>0.02398369109005874</v>
       </c>
       <c r="CQ84" s="0">
-        <v>0.16254876462938867</v>
+        <v>0.16254876462938866</v>
       </c>
       <c r="CR84" s="0">
         <v>0</v>
@@ -30646,7 +30645,7 @@
         <v>0</v>
       </c>
       <c r="T85" s="0">
-        <v>3.8721573448063889</v>
+        <v>3.8721573448063888</v>
       </c>
       <c r="U85" s="0">
         <v>0</v>
@@ -30871,7 +30870,7 @@
         <v>0.02398369109005874</v>
       </c>
       <c r="CQ85" s="0">
-        <v>0.032509752925877739</v>
+        <v>0.032509752925877738</v>
       </c>
       <c r="CR85" s="0">
         <v>0</v>
@@ -31041,7 +31040,7 @@
         <v>0</v>
       </c>
       <c r="AE86" s="0">
-        <v>0.20491803278688509</v>
+        <v>0.20491803278688508</v>
       </c>
       <c r="AF86" s="0">
         <v>0</v>
@@ -31299,7 +31298,7 @@
         <v>0</v>
       </c>
       <c r="DM86" s="0">
-        <v>3.8461538461538432</v>
+        <v>3.8461538461538431</v>
       </c>
       <c r="DN86" s="0">
         <v>1.3671874999999989</v>
@@ -31403,7 +31402,7 @@
         <v>0</v>
       </c>
       <c r="AE87" s="0">
-        <v>0.20491803278688509</v>
+        <v>0.20491803278688508</v>
       </c>
       <c r="AF87" s="0">
         <v>0</v>
@@ -31490,7 +31489,7 @@
         <v>0</v>
       </c>
       <c r="BH87" s="0">
-        <v>1.8908969210174012</v>
+        <v>1.8908969210174011</v>
       </c>
       <c r="BI87" s="0">
         <v>0</v>
@@ -31897,7 +31896,7 @@
         <v>0</v>
       </c>
       <c r="BW88" s="0">
-        <v>4.7807017543859614</v>
+        <v>4.7807017543859613</v>
       </c>
       <c r="BX88" s="0">
         <v>0</v>
@@ -32055,7 +32054,7 @@
         <v>4.5881036412154561</v>
       </c>
       <c r="G89" s="0">
-        <v>4.7676282051282009</v>
+        <v>4.7676282051282008</v>
       </c>
       <c r="H89" s="0">
         <v>6.5092340296699911</v>
@@ -32073,7 +32072,7 @@
         <v>6.8726691529035637</v>
       </c>
       <c r="M89" s="0">
-        <v>2.6195426195426173</v>
+        <v>2.6195426195426172</v>
       </c>
       <c r="N89" s="0">
         <v>10.218068535825536</v>
@@ -32429,7 +32428,7 @@
         <v>5.4287358526759979</v>
       </c>
       <c r="K90" s="0">
-        <v>0.17103762827822106</v>
+        <v>0.17103762827822105</v>
       </c>
       <c r="L90" s="0">
         <v>3.5695258391049514</v>
@@ -32776,7 +32775,7 @@
         <v>0.12148397346042415</v>
       </c>
       <c r="F91" s="0">
-        <v>0.26685030558664003</v>
+        <v>0.26685030558664002</v>
       </c>
       <c r="G91" s="0">
         <v>0.32051282051282021</v>
@@ -33022,7 +33021,7 @@
         <v>0</v>
       </c>
       <c r="CJ91" s="0">
-        <v>0.031625553447185297</v>
+        <v>0.031625553447185296</v>
       </c>
       <c r="CK91" s="0">
         <v>0</v>
@@ -33147,7 +33146,7 @@
         <v>6.4789585225552475</v>
       </c>
       <c r="I92" s="0">
-        <v>1.2292358803986701</v>
+        <v>1.22923588039867</v>
       </c>
       <c r="J92" s="0">
         <v>8.8624592365240655</v>
@@ -34613,7 +34612,7 @@
         <v>0</v>
       </c>
       <c r="O96" s="0">
-        <v>1.0282776349614387</v>
+        <v>1.0282776349614386</v>
       </c>
       <c r="P96" s="0">
         <v>0.01706193482340896</v>
@@ -36070,7 +36069,7 @@
         <v>4.0123456790123422</v>
       </c>
       <c r="R100" s="0">
-        <v>1.3774104683195581</v>
+        <v>1.377410468319558</v>
       </c>
       <c r="S100" s="0">
         <v>0</v>
